--- a/docs/projects-inventory.xlsx
+++ b/docs/projects-inventory.xlsx
@@ -39,10 +39,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00006100"/>
     </font>
   </fonts>
   <fills count="7">
@@ -64,12 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,25 +118,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -579,14 +579,14 @@
           <t>Asyut Western Road - Asyut Gate October</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>(unchanged — client to confirm)</t>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Asyut Western Road – October Gate, Asyut (confirmed by client 2026-09-15)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Yes — "بوابة أسيوط أكتوبر" rendered as "Asyut Gate October"; meaning/word order unclear. Confirm intended English.</t>
+          <t>Yes — "بوابة أسيوط أكتوبر" rendered as "Asyut Gate October"; meaning/word order unclear. Confirm intended English. → RESOLVED: English name confirmed by client 2026-09-15.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -594,7 +594,7 @@
           <t>../imgs/slider.jpg</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -606,7 +606,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish. Confirm English name. Also confirm whether unused imgs/slider1–3.jpg belong to this project (HTML references "slider.jpg").</t>
+          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish. Also confirm whether unused imgs/slider1–3.jpg belong to this project (HTML references "slider.jpg").</t>
         </is>
       </c>
     </row>
@@ -624,14 +624,14 @@
           <t>Asyut Western Road - Fayoum Silos &amp; Checkpoint</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>(unchanged — client to confirm)</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Asyut Western Road – Fayoum Silos &amp; Traffic Checkpoint (confirmed by client 2026-09-15)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Yes — "مرور الفيوم" (Fayoum traffic point) rendered as "Checkpoint"; Arabic word order (Silos, then Fayoum traffic) differs. Confirm wording.</t>
+          <t>Yes — "مرور الفيوم" (Fayoum traffic point) rendered as "Checkpoint"; Arabic word order (Silos, then Fayoum traffic) differs. Confirm wording. → RESOLVED: English name confirmed by client 2026-09-15.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -639,7 +639,7 @@
           <t>../imgs/project2.jpg</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -651,7 +651,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish. Confirm English name.</t>
+          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
           <t>../imgs/project3.jpg</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -729,7 +729,7 @@
           <t>../imgs/project8.jpg</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -759,14 +759,14 @@
           <t>Future of Egypt Project</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>(unchanged — client to confirm)</t>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Future of Egypt Project (confirmed by client 2026-09-15)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>No — optional: confirm whether the client prefers a transliterated official name.</t>
+          <t>No — optional: confirm whether the client prefers a transliterated official name. → RESOLVED: English name confirmed by client 2026-09-15.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
           <t>../imgs/مستقبل_مصر.jpg</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -804,14 +804,14 @@
           <t>Talbia Axis</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>(unchanged — client to confirm)</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Talbia Axis (confirmed by client 2026-09-15)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>No — transliteration variant ("Talbia" / "Talbiya"); confirm preferred spelling.</t>
+          <t>No — transliteration variant ("Talbia" / "Talbiya"); confirm preferred spelling. → RESOLVED: English name confirmed by client 2026-09-15.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -819,7 +819,7 @@
           <t>../imgs/project4.jpg</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -864,7 +864,7 @@
           <t>../imgs/project5.jpg</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -909,7 +909,7 @@
           <t>../imgs/project9.jpg</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -954,7 +954,7 @@
           <t>../imgs/محور_عمرو_بنالعاص.jpg</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -984,7 +984,7 @@
           <t>Ring Road Development - Qalyoub Exit</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Ring Road Development &amp; Widening - Qalyoub Exit</t>
         </is>
@@ -999,7 +999,7 @@
           <t>../imgs/project6.jpg</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1029,7 +1029,7 @@
           <t>Ring Road Development - Mansouria Exit</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Ring Road Development &amp; Widening - Mansouria (Haram) Exit</t>
         </is>
@@ -1044,7 +1044,7 @@
           <t>../imgs/project7.jpg</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1074,7 +1074,7 @@
           <t>Ring Road Development - Bahtim</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Ring Road Development &amp; Widening - Bahtim</t>
         </is>
@@ -1089,7 +1089,7 @@
           <t>../imgs/project11.jpg</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1119,7 +1119,7 @@
           <t>Cairo University Roads - Sheikh Zayed Branch</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Cairo University Roads Development &amp; Widening - Sheikh Zayed Branch</t>
         </is>
@@ -1134,7 +1134,7 @@
           <t>../imgs/project12.jpg</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1164,7 +1164,7 @@
           <t>El-Masallat Road - Suez</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>El-Mothallath (Triangle) Road Development &amp; Widening - Suez</t>
         </is>
@@ -1179,7 +1179,7 @@
           <t>../imgs/project13.jpg</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1209,7 +1209,7 @@
           <t>Suez - Sokhna Road</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Suez - Sokhna Road Development &amp; Widening</t>
         </is>
@@ -1224,7 +1224,7 @@
           <t>../imgs/project14.jpg</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1254,7 +1254,7 @@
           <t>October Western Sector Maintenance</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>October Western Sector Development &amp; Maintenance</t>
         </is>
@@ -1269,7 +1269,7 @@
           <t>../imgs/الطريق_الغربي_اكتوبر.jpg</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1299,7 +1299,7 @@
           <t>October Southern Districts Maintenance</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>October Southern Districts Development &amp; Maintenance</t>
         </is>
@@ -1314,7 +1314,7 @@
           <t>../imgs/project16.jpg</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1344,14 +1344,14 @@
           <t>October West Sumed Maintenance</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>October West Sumed Development &amp; Maintenance (transliteration "Sumed" still to confirm)</t>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>October West Sumed Development &amp; Maintenance (confirmed by client 2026-09-15)</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Yes — "سوميد" transliterated as "Sumed"; confirm the spelling the client/owner uses.</t>
+          <t>Yes — "سوميد" transliterated as "Sumed"; confirm the spelling the client/owner uses. → RESOLVED: English name confirmed by client 2026-09-15.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1359,7 +1359,7 @@
           <t>../imgs/project17.jpg</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish. Confirm English name.</t>
+          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish.</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
           <t>October Northern Sector Maintenance</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>October Northern Sector Development &amp; Maintenance</t>
         </is>
@@ -1404,7 +1404,7 @@
           <t>../imgs/project18.jpg</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1434,7 +1434,7 @@
           <t>Mokattam Maintenance</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Mokattam Development &amp; Maintenance</t>
         </is>
@@ -1449,7 +1449,7 @@
           <t>../imgs/project19.jpg</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1479,7 +1479,7 @@
           <t>Zahraa Maadi Maintenance</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Zahraa Maadi Development &amp; Maintenance</t>
         </is>
@@ -1494,7 +1494,7 @@
           <t>../imgs/project20.jpg</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1524,7 +1524,7 @@
           <t>Maadi Nerco Maintenance</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Maadi Nerco Development &amp; Maintenance</t>
         </is>
@@ -1539,7 +1539,7 @@
           <t>../imgs/project21.jpg</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1569,7 +1569,7 @@
           <t>Natrn Valley Maintenance</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Wadi El Natrun Development &amp; Maintenance</t>
         </is>
@@ -1584,7 +1584,7 @@
           <t>../imgs/وادي_النطرون.jpg</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1614,14 +1614,14 @@
           <t>Brick Factory - New Capital (R1 &amp; R2)</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>(unchanged — client to confirm)</t>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Brick Factory – New Capital (R1 &amp; R2) (confirmed by client 2026-09-15)</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Yes — English adds "New"; Arabic says only "العاصمة" (the Capital). Confirm it is the New Administrative Capital.</t>
+          <t>Yes — English adds "New"; Arabic says only "العاصمة" (the Capital). Confirm it is the New Administrative Capital. → RESOLVED: English name confirmed by client 2026-09-15.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1629,7 +1629,7 @@
           <t>../imgs/factory1.jpg</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish. Confirm English name.</t>
+          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish.</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
           <t>../imgs/factory2.jpg</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1719,7 +1719,7 @@
           <t>../imgs/factory3.jpg</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1749,14 +1749,14 @@
           <t>Brick Factory - 15 May City</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>(unchanged — client to confirm)</t>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Brick Factory – 15th of May City (confirmed by client 2026-09-15)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>No (minor) — commonly written "15th of May City".</t>
+          <t>No (minor) — commonly written "15th of May City". → RESOLVED: English name confirmed by client 2026-09-15.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1764,7 +1764,7 @@
           <t>../imgs/factory4.jpg</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>No – 404</t>
         </is>
@@ -1828,11 +1828,11 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>English names corrected</t>
+          <t>English names corrected or client-confirmed</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/projects-inventory.xlsx
+++ b/docs/projects-inventory.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects'!$A$1:$I$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Projects'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1780,63 +1780,105 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>مصنع الطوب في القطامية بالأسمرات</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Brick Factory - Katameya (Al-Asmarat)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Brick Factory – Katameya (Al-Asmarat) (added by client 2026-09-17)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>No — name supplied by the client in both languages (2026-09-17).</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>— (new project; not in the original site)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>No – none yet</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Total projects</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="C31" s="9" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Images found</t>
         </is>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C32" s="10" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Images missing (404)</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
       <c r="B33" s="8" t="inlineStr">
         <is>
+          <t>Images missing (404 or none yet)</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>Translation issues flagged "Yes"</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C34" s="11" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>English names corrected or client-confirmed</t>
         </is>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>20</v>
-      </c>
-    </row>
+      <c r="C35" s="11" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36"/>
   </sheetData>
-  <autoFilter ref="A1:I28"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/docs/projects-inventory.xlsx
+++ b/docs/projects-inventory.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects'!$A$1:$I$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Projects'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1825,60 +1825,239 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>مصنع الطوب في السياحية أكتوبر</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Brick Factory - Al-Seyahia, 6th of October</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Brick Factory – Al-Seyahia, 6th of October (added by client 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>No — name supplied by the client in both languages (2026-09-18).</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>— (new project; not in the original site)</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>No – none yet</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish.</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Total projects</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>28</v>
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>تطوير طريق الدولي الساحلي</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>International Coastal Road Development</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>International Coastal Road Development (added by client 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>No — name supplied by the client in both languages (2026-09-18).</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>— (new project; not in the original site)</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Yes – client photos 197, 199, 202 on the card; 198, 200 in the gallery (media batch 2, 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp copies, 960×1280 portrait; the 4:3 crops are 960×720 (202: 760×570), below 1200×900. 201 not used (photographer's shadow).</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Optional: the original photos (sent as documents), for sharper cards.</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Images found</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>4</v>
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>رفع كفاءة طريق محلة دمنة – المنصورة</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Mahallet Damana - Mansoura Road Upgrade</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Mahallet Damana – Mansoura Road Upgrade (added by client 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>No — name supplied by the client in both languages (2026-09-18).</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>— (new project; not in the original site)</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>No – none yet</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish.</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Images missing (404 or none yet)</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Translation issues flagged "Yes"</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>رفع كفاءة طريق فارسكور – شربين – دمياط</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Faraskur - Sherbin - Damietta Road Upgrade</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Faraskur – Sherbin – Damietta Road Upgrade (added by client 2026-09-18)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>No — name supplied by the client in both languages (2026-09-18).</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>— (new project; not in the original site)</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>No – none yet</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Project photo(s): 1–3 per project, 4:3, min 1200×900, with permission to publish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>Total projects</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Images found</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Images missing (404 or none yet)</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Translation issues flagged "Yes"</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
           <t>English names corrected or client-confirmed</t>
         </is>
       </c>
-      <c r="C35" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="C39" s="11" t="n">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:I33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -1953,7 +2132,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rows 1–5 Road &amp; Infrastructure · 6–9 Bridge &amp; Axis · 10–23 Development &amp; Maintenance · 24–27 Brick Factories</t>
+          <t>Rows 1–5 Road &amp; Infrastructure · 6–9 Bridge &amp; Axis · 10–23 Development &amp; Maintenance · 24–27 Brick Factories · added by the client: 28 and 29 Brick Factories (2026-09-17, 2026-09-18), 30–32 Development &amp; Maintenance (2026-09-18)</t>
         </is>
       </c>
     </row>
